--- a/assets/translations/Bengali.Bengal.bn-BD.xlsx
+++ b/assets/translations/Bengali.Bengal.bn-BD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mushfiqulanwarsiraji/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2118B37-0A8B-8149-AE10-B4467E627AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E20F815-034C-D34D-88F9-BFC003C8F68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="19860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="1" r:id="rId1"/>
@@ -386,13 +386,7 @@
     <t>আলো আমাদের দেহের জন্য খুব গুরুত্বপূর্ণ—এটা দেহঘড়ির সময়, ঘুম, মেজাজ আর ভাবনা-চিন্তার ক্ষমতার ওপর সরাসরি প্রভাব ফেলে।</t>
   </si>
   <si>
-    <t>শুধু আলো উজ্জ্বল কি না, তা নয়। কখন আলো পড়ছে, আর সেই আলোর ধরন কেমন—দুটোই গুরুত্বপূর্ণ।</t>
-  </si>
-  <si>
     <t>সকাল ও দিনের বেলায় সূর্যের আলো শরীরের জন্য ভালো; রাতে বেশি আলো থাকলে ঘুম ও দেহঘড়ির ছন্দ নষ্ট হতে পারে।</t>
-  </si>
-  <si>
-    <t>সন্ধ্যার পর কম আলো, আর ঘুমের সময় অন্ধকার—এটাই সুস্থ আলো–অন্ধকারের নিয়ম।</t>
   </si>
   <si>
     <t>স্বাস্থ্যকর জীবনযাপনের জন্য সঠিক খাবার, ব্যায়াম ও ভালো ঘুম যেমন জরুরি, তেমনি আলোয় থাকা–না থাকা ঠিকভাবে সামলানোও জরুরি।</t>
@@ -519,12 +513,6 @@
   </si>
   <si>
     <t>প্রতিটি তরঙ্গদৈর্ঘ্যে আলো কত শক্তি ছাড়ে—এই বিবরণ দিয়ে আলোর উৎসকে চেনা যায়। এই শক্তিকেই তীব্রতা বলা হয়। পদার্থবিদরা তীব্রতা মাপেন; জীববিজ্ঞানী ও মনোবিজ্ঞানীরা দেখেন—এই তীব্রতা শরীর-মনের নানা প্রক্রিয়ায় কী প্রভাব ফেলে।</t>
-  </si>
-  <si>
-    <t>দিনের আলোতে অনেক রঙের (তরঙ্গদৈর্ঘ্যের) শক্তি থাকে—রংধনুর সব রঙ আলাদা করা যায়।</t>
-  </si>
-  <si>
-    <t>দিনের আলো—সরাসরি সূর্যালোক ও আকাশের ছড়ানো আলোর মিশ্রণ—দৃশ্যমান সব তরঙ্গদৈর্ঘ্যই থাকে। সময় আর আবহাওয়া বদলালে এই গঠনও বদলে যায়; তাই দিনের আলোর রঙও বদলে দেখা দেয়।</t>
   </si>
   <si>
     <t>আলোর উৎসভেদে তৈরি হওয়া তরঙ্গদৈর্ঘ্য (রঙ) আলাদা হয়।</t>
@@ -667,6 +655,18 @@
   <si>
     <t xml:space="preserve">তথ্যসূত্র </t>
   </si>
+  <si>
+    <t>সন্ধ্যায় কম আলো, আর ঘুমের সময় অন্ধকার—সুস্থ আলো–অন্ধকারের ছন্দের অংশ।</t>
+  </si>
+  <si>
+    <t>আলো কতটা উজ্জ্বল শুধু তা নয়, কখন আলো পড়ছে আর কেমন আলো, দুটোই গুরুত্বপূর্ণ।</t>
+  </si>
+  <si>
+    <t>দিনের আলো—সরাসরি সূর্যালোক ও আকাশের ছড়ানো আলোর মিশ্রণ—দৃশ্যমান সব তরঙ্গদৈর্ঘ্যই ধারণ করে। সময় আর আবহাওয়া বদলালে এই গঠনও বদলে যায়; তাই দিনের আলোর রঙও বদলে দেখা দেয়।</t>
+  </si>
+  <si>
+    <t>দিনের আলো বহু তরঙ্গদৈর্ঘ্যজুড়ে শক্তি বহন করে—তাই এটাকে রংধনুর সব রঙে আলাদা করা যায়।</t>
+  </si>
 </sst>
 </file>
 
@@ -677,6 +677,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -805,11 +812,6 @@
       <name val="Shonar Bangla"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Shonar Bangla"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="1"/>
@@ -825,7 +827,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,8 +840,14 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -858,21 +866,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -906,93 +899,97 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -29228,76 +29225,76 @@
     <col min="2" max="2" width="25.1640625" style="12" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="42.33203125" customWidth="1"/>
-    <col min="6" max="6" width="24.5" style="28" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="26" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" customWidth="1"/>
-    <col min="8" max="8" width="27.6640625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="27.6640625" style="30" customWidth="1"/>
     <col min="9" max="9" width="42.33203125" customWidth="1"/>
-    <col min="10" max="10" width="50.1640625" style="27" customWidth="1"/>
+    <col min="10" max="10" width="50.1640625" style="25" customWidth="1"/>
     <col min="11" max="27" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="22" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:27" s="20" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36" t="s">
-        <v>150</v>
+      <c r="B1" s="34" t="s">
+        <v>148</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="33" t="s">
-        <v>204</v>
+      <c r="D1" s="31" t="s">
+        <v>200</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="86" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>10</v>
+      <c r="C2" s="17">
+        <v>1</v>
       </c>
-      <c r="H1" s="31" t="s">
-        <v>116</v>
+      <c r="D2" s="17">
+        <v>1</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>11</v>
+      <c r="E2" s="17" t="s">
+        <v>13</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="F2" s="32" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" ht="121" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="19">
-        <v>1</v>
-      </c>
-      <c r="D2" s="19">
-        <v>1</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="29" t="s">
-        <v>151</v>
+      <c r="H2" s="27" t="s">
+        <v>149</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>152</v>
+      <c r="J2" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -29317,804 +29314,804 @@
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
     </row>
-    <row r="3" spans="1:27" ht="121" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="17">
+        <v>2</v>
+      </c>
+      <c r="D3" s="17">
+        <v>2</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="121" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="17">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17">
+        <v>3</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="19">
-        <v>2</v>
+      <c r="G4" s="22" t="s">
+        <v>20</v>
       </c>
-      <c r="D3" s="19">
-        <v>2</v>
+      <c r="H4" s="27" t="s">
+        <v>153</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="I4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="103" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="17">
+        <v>4</v>
+      </c>
+      <c r="D5" s="17">
+        <v>4</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="120" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="17">
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="81" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="17">
+        <v>6</v>
+      </c>
+      <c r="D7" s="17">
+        <v>6</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="86" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="17">
+        <v>7</v>
+      </c>
+      <c r="D8" s="17">
+        <v>7</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="86" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="17">
+        <v>8</v>
+      </c>
+      <c r="D9" s="17">
+        <v>8</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="61" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="17">
+        <v>9</v>
+      </c>
+      <c r="D10" s="17">
+        <v>9</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="17">
+        <v>10</v>
+      </c>
+      <c r="D11" s="17">
+        <v>10</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="103" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="17">
+        <v>11</v>
+      </c>
+      <c r="D12" s="17">
+        <v>11</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="81" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="17">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17">
+        <v>12</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="81" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="17">
+        <v>13</v>
+      </c>
+      <c r="D14" s="17">
+        <v>13</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="86" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="17">
+        <v>14</v>
+      </c>
+      <c r="D15" s="17">
+        <v>14</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="69" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="17">
+        <v>15</v>
+      </c>
+      <c r="D16" s="17">
+        <v>15</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="81" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="17">
         <v>16</v>
       </c>
-      <c r="F3" s="34" t="s">
-        <v>121</v>
+      <c r="D17" s="17">
+        <v>16</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="E17" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="61" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="17">
         <v>17</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>153</v>
+      <c r="D18" s="17">
+        <v>17</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="E18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="69" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="17">
         <v>18</v>
       </c>
-      <c r="J3" s="25" t="s">
-        <v>154</v>
+      <c r="D19" s="17">
+        <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" ht="141" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>12</v>
+      <c r="E19" s="17" t="s">
+        <v>65</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>120</v>
+      <c r="F19" s="32" t="s">
+        <v>137</v>
       </c>
-      <c r="C4" s="19">
-        <v>3</v>
+      <c r="G19" s="22" t="s">
+        <v>66</v>
       </c>
-      <c r="D4" s="19">
-        <v>3</v>
+      <c r="H19" s="27" t="s">
+        <v>181</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="I19" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="69" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="17">
         <v>19</v>
       </c>
-      <c r="F4" s="35" t="s">
-        <v>122</v>
+      <c r="D20" s="17">
+        <v>19</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="E20" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="121" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="17">
         <v>20</v>
       </c>
-      <c r="H4" s="29" t="s">
-        <v>155</v>
+      <c r="D21" s="17">
+        <v>20</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="E21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="69" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="17">
         <v>21</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>156</v>
+      <c r="D22" s="17">
+        <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" ht="103" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
-        <v>12</v>
+      <c r="E22" s="17" t="s">
+        <v>75</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>120</v>
+      <c r="F22" s="32" t="s">
+        <v>141</v>
       </c>
-      <c r="C5" s="19">
-        <v>4</v>
+      <c r="G22" s="22" t="s">
+        <v>76</v>
       </c>
-      <c r="D5" s="19">
-        <v>4</v>
+      <c r="H22" s="27" t="s">
+        <v>187</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="I22" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="81" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="17">
         <v>22</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>123</v>
+      <c r="D23" s="17">
+        <v>22</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="E23" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="61" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="17">
         <v>23</v>
       </c>
-      <c r="H5" s="29" t="s">
-        <v>157</v>
+      <c r="D24" s="17">
+        <v>23</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="E24" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="61" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="17">
         <v>24</v>
       </c>
-      <c r="J5" s="25" t="s">
-        <v>158</v>
+      <c r="D25" s="17">
+        <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" ht="121" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>12</v>
+      <c r="E25" s="17" t="s">
+        <v>85</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>120</v>
+      <c r="F25" s="33" t="s">
+        <v>145</v>
       </c>
-      <c r="C6" s="19">
-        <v>5</v>
+      <c r="G25" s="22" t="s">
+        <v>86</v>
       </c>
-      <c r="D6" s="19">
-        <v>5</v>
+      <c r="H25" s="27" t="s">
+        <v>193</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="I25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="103" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="17">
         <v>25</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>124</v>
+      <c r="D26" s="17">
+        <v>25</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="E26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="141" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="17">
         <v>26</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>159</v>
+      <c r="D27" s="17">
+        <v>26</v>
       </c>
-      <c r="I6" s="19" t="s">
-        <v>27</v>
+      <c r="E27" s="17" t="s">
+        <v>91</v>
       </c>
-      <c r="J6" s="25" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="19">
-        <v>6</v>
-      </c>
-      <c r="D7" s="19">
-        <v>6</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="19">
-        <v>7</v>
-      </c>
-      <c r="D8" s="19">
-        <v>7</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="86" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="19">
-        <v>8</v>
-      </c>
-      <c r="D9" s="19">
-        <v>8</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="61" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="19">
-        <v>9</v>
-      </c>
-      <c r="D10" s="19">
-        <v>9</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="121" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="19">
-        <v>10</v>
-      </c>
-      <c r="D11" s="19">
-        <v>10</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="103" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C12" s="19">
-        <v>11</v>
-      </c>
-      <c r="D12" s="19">
-        <v>11</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="19">
-        <v>12</v>
-      </c>
-      <c r="D13" s="19">
-        <v>12</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="19">
-        <v>13</v>
-      </c>
-      <c r="D14" s="19">
-        <v>13</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" s="19">
-        <v>14</v>
-      </c>
-      <c r="D15" s="19">
-        <v>14</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="69" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="19">
-        <v>15</v>
-      </c>
-      <c r="D16" s="19">
-        <v>15</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" s="25" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="19">
-        <v>16</v>
-      </c>
-      <c r="D17" s="19">
-        <v>16</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="61" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="19">
-        <v>17</v>
-      </c>
-      <c r="D18" s="19">
-        <v>17</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="81" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="19">
-        <v>18</v>
-      </c>
-      <c r="D19" s="19">
-        <v>18</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="69" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" s="19">
-        <v>19</v>
-      </c>
-      <c r="D20" s="19">
-        <v>19</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="161" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="19">
-        <v>20</v>
-      </c>
-      <c r="D21" s="19">
-        <v>20</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="81" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="19">
-        <v>21</v>
-      </c>
-      <c r="D22" s="19">
-        <v>21</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="101" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="19">
-        <v>22</v>
-      </c>
-      <c r="D23" s="19">
-        <v>22</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="61" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="19">
-        <v>23</v>
-      </c>
-      <c r="D24" s="19">
-        <v>23</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="81" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="19">
-        <v>24</v>
-      </c>
-      <c r="D25" s="19">
-        <v>24</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="35" t="s">
+      <c r="F27" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="G25" s="24" t="s">
-        <v>86</v>
+      <c r="G27" s="22" t="s">
+        <v>92</v>
       </c>
-      <c r="H25" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J25" s="25" t="s">
+      <c r="H27" s="27" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="121" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="19">
-        <v>25</v>
-      </c>
-      <c r="D26" s="19">
-        <v>25</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="161" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="19">
-        <v>26</v>
-      </c>
-      <c r="D27" s="19">
-        <v>26</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="J27" s="25" t="s">
-        <v>201</v>
+      <c r="J27" s="23" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -30142,7 +30139,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="14" t="s">
         <v>103</v>
       </c>
       <c r="B2" s="13" t="s">
@@ -30161,24 +30158,24 @@
       <c r="A4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>112</v>
+      <c r="B4" s="36" t="s">
+        <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>114</v>
+      <c r="B6" s="37" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -30186,7 +30183,7 @@
         <v>99</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -31211,15 +31208,15 @@
         <v>101</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>205</v>
+      <c r="B3" s="35" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
